--- a/output/pdf_financials_xlsx/LLL.xlsx
+++ b/output/pdf_financials_xlsx/LLL.xlsx
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.205239</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.205239</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.205239</v>
       </c>
     </row>
     <row r="93">
@@ -3341,7 +3341,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4316,7 +4320,11 @@
           <t>Reserve 9</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.205239</v>
       </c>

--- a/output/pdf_financials_xlsx/LLL.xlsx
+++ b/output/pdf_financials_xlsx/LLL.xlsx
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.151743</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.026539</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001687</v>
       </c>
     </row>
     <row r="35">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.151743</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.026539</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001687</v>
       </c>
     </row>
     <row r="37">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.296743</v>
+        <v>0.145</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.333111</v>
+        <v>0.306572</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.550115</v>
+        <v>0.548428</v>
       </c>
     </row>
     <row r="49">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/LLL.xlsx
+++ b/output/pdf_financials_xlsx/LLL.xlsx
@@ -898,10 +898,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-2.247396</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.983341</v>
@@ -2158,10 +2156,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-2.247396</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.983341</v>
@@ -2176,16 +2172,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0.012979</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.009462999999999999</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.012824</v>
       </c>
     </row>
     <row r="101">
@@ -2194,10 +2188,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -2212,10 +2204,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2230,10 +2220,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -2248,10 +2236,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0</v>
@@ -2266,10 +2252,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -2284,10 +2268,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0</v>
@@ -2302,10 +2284,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -2320,10 +2300,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2338,10 +2316,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2356,16 +2332,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0.233337</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.253569</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.42343</v>
       </c>
     </row>
     <row r="111">
@@ -2374,10 +2348,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2392,10 +2364,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2410,10 +2380,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2428,10 +2396,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2446,10 +2412,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2464,10 +2428,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2482,10 +2444,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2500,10 +2460,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2518,10 +2476,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-3.45</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.329847</v>
@@ -2536,10 +2492,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2554,10 +2508,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -2572,10 +2524,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2590,10 +2540,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2608,10 +2556,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2626,10 +2572,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2644,10 +2588,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2684,10 +2626,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -2702,10 +2642,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>3.685825</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.334301</v>
@@ -2742,10 +2680,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -2760,10 +2696,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.124016</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.125204</v>
@@ -2800,10 +2734,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2818,10 +2750,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.111809</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.129658</v>
@@ -2841,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4797,10 +4727,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="5" t="n">
+        <v>-2.247396</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>-0.983341</v>
@@ -4826,10 +4754,8 @@
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>0.145</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0.306572</v>
@@ -4855,10 +4781,8 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="5" t="n">
+        <v>-0.408872</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>-0.665479</v>
@@ -4884,10 +4808,8 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="5" t="n">
+        <v>0.388766</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0.650011</v>
@@ -4912,11 +4834,13 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.233337</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>0.253569</v>
@@ -4941,11 +4865,13 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.012979</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>0.009462999999999999</v>
@@ -5000,10 +4926,8 @@
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="5" t="n">
+        <v>1.797165</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0.231083</v>
@@ -5029,10 +4953,8 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="5" t="n">
+        <v>0.00029</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>0.009931000000000001</v>
@@ -5062,10 +4984,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>-0.111809</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>-0.129658</v>
@@ -5091,10 +5011,8 @@
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>3.7</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>0.353201</v>
@@ -5120,10 +5038,8 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E76" s="5" t="n">
+        <v>-0.014175</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>-0.0189</v>
@@ -5153,10 +5069,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="5" t="n">
+        <v>3.685825</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>0.334301</v>
@@ -5215,10 +5129,8 @@
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="5" t="n">
+        <v>0.027727</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>0.151743</v>
@@ -5244,16 +5156,167 @@
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="5" t="n">
+        <v>0.151743</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>0.026539</v>
       </c>
       <c r="G80" s="5" t="n">
         <v>0.001687</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Adjustments for non‐cash items</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Unrealized foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>-0.103016</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.009682</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Adjustments for non‐cash items</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Equity loss on investments</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>0.069938</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.068215</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Loans advanced                                                                                         ‐           (2,450,000)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Investments made</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.329847</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Loans advanced                                                                                         ‐           (2,450,000)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.329847</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.124016</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-0.125204</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
